--- a/data/ascentmonthly.xlsx
+++ b/data/ascentmonthly.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03ADDA5-7B70-4AF6-B0E8-9C9DFA9FADDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542D7CAF-F4BE-4461-9416-6D317A643058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -387,13 +387,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -418,8 +418,11 @@
       <c r="H1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -444,8 +447,11 @@
       <c r="H2">
         <v>10145</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -470,8 +476,11 @@
       <c r="H3">
         <v>6927</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3">
+        <v>9363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -496,8 +505,11 @@
       <c r="H4">
         <v>7298</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -522,8 +534,11 @@
       <c r="H5">
         <v>10988</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5">
+        <v>16224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -548,8 +563,11 @@
       <c r="H6">
         <v>11989</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6">
+        <v>10913</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -574,8 +592,12 @@
       <c r="H7">
         <v>12718</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7">
+        <f>13004-910</f>
+        <v>12094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -600,8 +622,12 @@
       <c r="H8">
         <v>12895</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8">
+        <f>12831-3307</f>
+        <v>9524</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -627,7 +653,7 @@
         <v>9934</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -653,7 +679,7 @@
         <v>6920</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -679,7 +705,7 @@
         <v>9143</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -705,7 +731,7 @@
         <v>10742</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
